--- a/hardware/hexpansion_bom.xlsx
+++ b/hardware/hexpansion_bom.xlsx
@@ -550,14 +550,16 @@
         </is>
       </c>
       <c r="J5" s="6" t="n"/>
-      <c r="K5" s="7" t="n"/>
+      <c r="K5" s="7" t="n">
+        <v>1.27</v>
+      </c>
       <c r="L5" s="8">
         <f>IF(G5="Y",F5*K5,0)</f>
         <v/>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>RP2350A with 2MB flash stacked in package (on QSPI CS0) - no external flash needed. Copy Raspberry Pi RP2350 hardware design guide minimal design. Firmware: PICO_FLASH_SIZE_BYTES = 2MB</t>
+          <t>RP2350A with 2MB flash stacked in package (on QSPI CS0) - no external flash needed. Copy Raspberry Pi RP2350 hardware design guide minimal design. Firmware: PICO_FLASH_SIZE_BYTES = 2MB. Unit cost: GBP 1.00 converted at 1.27 USD/GBP</t>
         </is>
       </c>
     </row>

--- a/hardware/hexpansion_bom.xlsx
+++ b/hardware/hexpansion_bom.xlsx
@@ -406,7 +406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="15" min="1" max="2"/>
@@ -513,26 +513,26 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>C1,C2,C3,C4,C5,C6,C7,C8,C9,C10,C11,C12,C19,C20,C27,C28,C30,C32</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Microcontroller</t>
+          <t>Decoupling</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>RP2354A</t>
+          <t>CL05B104KO5NNNC (100nF)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>QFN-60 7x7</t>
+          <t>C0402</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
@@ -541,29 +541,27 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>C41378174</t>
+          <t>C1525</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="n"/>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>16407331</v>
+      </c>
       <c r="K5" s="7" t="n">
-        <v>1.27</v>
+        <v>0.006</v>
       </c>
       <c r="L5" s="8">
         <f>IF(G5="Y",F5*K5,0)</f>
         <v/>
       </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>RP2350A with 2MB flash stacked in package (on QSPI CS0) - no external flash needed. Copy Raspberry Pi RP2350 hardware design guide minimal design. Firmware: PICO_FLASH_SIZE_BYTES = 2MB. Unit cost: GBP 1.00 converted at 1.27 USD/GBP</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="23.85" customHeight="1" s="15">
+      <c r="M5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="15">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Core</t>
@@ -571,45 +569,53 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>C13,C14,C15,C31</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>QSPI PSRAM</t>
+          <t>Regulator caps</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>APS6404L-3SQR-ZR (8MB)</t>
+          <t>CL05A475MP5NRNC (4.7uF)</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>SOP-8</t>
+          <t>C0402</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="7" t="n"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>C23733</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>964426</v>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>0.0192</v>
+      </c>
       <c r="L6" s="8">
         <f>IF(G6="Y",F6*K6,0)</f>
         <v/>
       </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>Footprint only; hand-solder if wanted (SOP-8, 1.27mm pitch - confirm SOP-8 not USON variant). Shares QSPI SCLK/SD0-3 with the RP2354A internal flash; CS on GPIO0 (QMI CS1; 8 is microSD and 19 is HSTX) with 10k pull-up (fit even when U6 is not); 100nF decoupling. bom.csv lists LCSC C3040877 - avoid -SN variant (much pricier)</t>
-        </is>
-      </c>
+      <c r="M6" s="3" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="15">
       <c r="A7" s="3" t="inlineStr">
@@ -619,45 +625,53 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Y1</t>
+          <t>C16,C21,C23,C25</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Crystal</t>
+          <t>Bulk / regulator caps</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>12MHz</t>
+          <t>CL10A106KP8NNNC (10uF)</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>3.2x2.5mm</t>
+          <t>C0603</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="7" t="n"/>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>C19702</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>5302559</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>0.0824</v>
+      </c>
       <c r="L7" s="8">
         <f>IF(G7="Y",F7*K7,0)</f>
         <v/>
       </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>Load caps per crystal datasheet</t>
-        </is>
-      </c>
+      <c r="M7" s="3" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="15">
       <c r="A8" s="3" t="inlineStr">
@@ -667,36 +681,48 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>R_XOUT</t>
+          <t>C17,C18</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Crystal series resistor</t>
+          <t>Crystal load caps</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>1k (per design guide)</t>
+          <t>0402CG150J500NT (15pF)</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>C0402</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="7" t="n"/>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>C1548</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>358497</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>0.0022</v>
+      </c>
       <c r="L8" s="8">
         <f>IF(G8="Y",F8*K8,0)</f>
         <v/>
@@ -711,41 +737,57 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>C_XTAL</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Crystal load caps</t>
+          <t>SWD debug (RPi 3-pin)</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Value per crystal CL</t>
+          <t>BM03B-SRSS-TB(LF)(SN) (SWD)</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>CONN-SMD-3P-P1.00_BM03B-SRSS-TB-LF-SN</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="7" t="n"/>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>C160389</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>8526</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <v>0.2686</v>
+      </c>
       <c r="L9" s="8">
         <f>IF(G9="Y",F9*K9,0)</f>
         <v/>
       </c>
-      <c r="M9" s="3" t="n"/>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Vertical (top-entry) JST-SH</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="15">
       <c r="A10" s="3" t="inlineStr">
@@ -760,17 +802,17 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Core regulator inductor</t>
+          <t>RP2350 core regulator inductor</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>3.3uH</t>
+          <t>AOTA-B201610S3R3-101-T (3.3uH)</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Per design guide</t>
+          <t>IND-SMD_L2.0-W1.6_AOTA-B201610S3R3-101-T</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
@@ -781,17 +823,29 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="7" t="n"/>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>C42411119</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>20758</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>0.2822</v>
+      </c>
       <c r="L10" s="8">
         <f>IF(G10="Y",F10*K10,0)</f>
         <v/>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>Per RP2350 datasheet minimal design</t>
+          <t>Part named in the RP2350 hardware design guide</t>
         </is>
       </c>
     </row>
@@ -803,45 +857,53 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>C_DEC</t>
+          <t>R1,R36,R37,R38,R39</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Decoupling caps</t>
+          <t>Resistor</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>100nF</t>
+          <t>0402WGF330JTCE (33R)</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>R0402</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="7" t="n"/>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>C25105</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>968914</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>0.001</v>
+      </c>
       <c r="L11" s="8">
         <f>IF(G11="Y",F11*K11,0)</f>
         <v/>
       </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>Approx count - confirm against design guide</t>
-        </is>
-      </c>
+      <c r="M11" s="3" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="15">
       <c r="A12" s="3" t="inlineStr">
@@ -851,162 +913,194 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>C_BULK</t>
+          <t>R2,R6,R40,R51</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Bulk / regulator caps</t>
+          <t>Resistor</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1uF - 4.7uF</t>
+          <t>0402WGF1001TCE (1k)</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>0402 / 0603</t>
+          <t>R0402</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="7" t="n"/>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>C11702</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>2610919</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>0.0011</v>
+      </c>
       <c r="L12" s="8">
         <f>IF(G12="Y",F12*K12,0)</f>
         <v/>
       </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>Approx count - confirm against design guide</t>
-        </is>
-      </c>
+      <c r="M12" s="3" t="n"/>
     </row>
     <row r="13" ht="23.85" customHeight="1" s="15">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>R3,R5,R7,R41,R42,R43,R44,R45,R46,R47</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>USB-C receptacle (programming / ext. power)</t>
+          <t>Resistor</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>USB-C 16-pin</t>
+          <t>0402WGF1002TCE (10k)</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>SMT + THT tabs</t>
+          <t>R0402</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="7" t="n"/>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>C25744</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>1256270</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>0.0029</v>
+      </c>
       <c r="L13" s="8">
         <f>IF(G13="Y",F13*K13,0)</f>
         <v/>
       </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>Shield tabs for strength on 1.0mm board</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="15">
+      <c r="M13" s="3" t="n"/>
+    </row>
+    <row r="14" ht="23.85" customHeight="1" s="15">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>R_CC</t>
+          <t>R4,R21,R22,R23,R24,R25,R26,R27,R28</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>CC pull-downs</t>
+          <t>Resistor</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>5.1k</t>
+          <t>0402WGF0000TCE (0R)</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>R0402</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="7" t="n"/>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>C17168</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>3956017</v>
+      </c>
+      <c r="K14" s="7" t="n">
+        <v>0.0011</v>
+      </c>
       <c r="L14" s="8">
         <f>IF(G14="Y",F14*K14,0)</f>
         <v/>
       </c>
-      <c r="M14" s="3" t="n"/>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>R4 = LS_A to RUN link (see schematic notes)</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>R_USB</t>
+          <t>SW1,SW2</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>USB series resistors</t>
+          <t>BOOTSEL + RESET buttons</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>27 ohm (per design guide)</t>
+          <t>TS-1088-AR02016 (BOOTSEL/RESET)</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>SW-SMD_L3.9-W3.0-P4.45</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
@@ -1017,10 +1111,22 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="7" t="n"/>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>C720477</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>877449</v>
+      </c>
+      <c r="K15" s="7" t="n">
+        <v>0.0557</v>
+      </c>
       <c r="L15" s="8">
         <f>IF(G15="Y",F15*K15,0)</f>
         <v/>
@@ -1030,27 +1136,27 @@
     <row r="16" ht="15" customHeight="1" s="15">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>D_USB</t>
+          <t>U1</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>USB ESD protection</t>
+          <t>Microcontroller, 2 MB flash in package</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Low-capacitance ESD array</t>
+          <t>RP2354A</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>SOT-23-6 or similar</t>
+          <t>QFN-60_L7.0-W7.0-P0.40-TL-EP3.4</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
@@ -1061,40 +1167,56 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="7" t="n"/>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>C41378174</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>6193</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>1.3097</v>
+      </c>
       <c r="L16" s="8">
         <f>IF(G16="Y",F16*K16,0)</f>
         <v/>
       </c>
-      <c r="M16" s="3" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="15">
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Unit price from JLC list; you quoted GBP 1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="23.85" customHeight="1" s="15">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>3.3V LDO from VBUS</t>
+          <t>QSPI PSRAM 8 MB (hand-solder)</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>LDO, &gt;=500mA</t>
+          <t>APS6404L-3SQR-SN</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>SOT-223 / SOT-23-5</t>
+          <t>SOIC-8_L4.9-W3.9-P1.27-LS6.0-BL</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
@@ -1102,43 +1224,59 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="7" t="n"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>C5333729</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>4.3423</v>
+      </c>
       <c r="L17" s="8">
         <f>IF(G17="Y",F17*K17,0)</f>
         <v/>
       </c>
-      <c r="M17" s="3" t="n"/>
-    </row>
-    <row r="18" ht="23.85" customHeight="1" s="15">
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>DNP. SOP-8 3.3 V part (the -ZR is USON-8). Buy separately for hand soldering</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="15">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>D_OR</t>
+          <t>Y1</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Power OR-ing (badge 3.3V vs USB 3.3V)</t>
+          <t>12 MHz crystal</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Ideal diode IC or Schottky pair</t>
+          <t>ABM8-272-T3 (12MHz)</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Various</t>
+          <t>CRYSTAL-SMD_4P-L3.2-W2.5-BL</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
@@ -1149,92 +1287,112 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H18" s="6" t="n"/>
-      <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="7" t="n"/>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>C20625731</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>18110</v>
+      </c>
+      <c r="K18" s="7" t="n">
+        <v>0.2938</v>
+      </c>
       <c r="L18" s="8">
         <f>IF(G18="Y",F18*K18,0)</f>
         <v/>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>Must prevent back-feed into badge rail</t>
+          <t>Crystal named in the RP2350 hardware design guide</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="15">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>USB-C input</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>C22,C24,C26</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>3.3V to 5V boost (HDMI pin 18)</t>
+          <t>Bulk caps</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Small boost converter</t>
+          <t>CL21A226MAQNNNE (22uF)</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Various</t>
+          <t>C0805</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="7" t="n"/>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>C45783</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>1734789</v>
+      </c>
+      <c r="K19" s="7" t="n">
+        <v>0.1185</v>
+      </c>
       <c r="L19" s="8">
         <f>IF(G19="Y",F19*K19,0)</f>
         <v/>
       </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>Optional - skip if monitor works without source 5V</t>
-        </is>
-      </c>
+      <c r="M19" s="3" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="15">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>USB-C input</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Current limit / resettable fuse for 5V</t>
+          <t>VBUS TVS</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>PTC or load switch</t>
+          <t>SMF5.0A</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0603 / SOT</t>
+          <t>SOD-123FL_L2.7-W1.8-LS3.8-RD</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
@@ -1245,44 +1403,52 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H20" s="6" t="n"/>
-      <c r="I20" s="6" t="n"/>
-      <c r="J20" s="6" t="n"/>
-      <c r="K20" s="7" t="n"/>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>C19077497</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>Preferred</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>969692</v>
+      </c>
+      <c r="K20" s="7" t="n">
+        <v>0.0273</v>
+      </c>
       <c r="L20" s="8">
         <f>IF(G20="Y",F20*K20,0)</f>
         <v/>
       </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>Optional with U4</t>
-        </is>
-      </c>
+      <c r="M20" s="3" t="n"/>
     </row>
     <row r="21" ht="23.85" customHeight="1" s="15">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>HDMI</t>
+          <t>USB-C input</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Mini HDMI (type C) receptacle</t>
+          <t>USB-C receptacle (sink)</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Mini HDMI SMT</t>
+          <t>TYPE-C 16PIN 2MD(073) (USB-C)</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>SMT + THT tabs</t>
+          <t>USB-C-SMD_TYPE-C-16PIN-2MD-073</t>
         </is>
       </c>
       <c r="F21" s="4" t="n">
@@ -1293,44 +1459,56 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H21" s="6" t="n"/>
-      <c r="I21" s="6" t="n"/>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="7" t="n"/>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>C2765186</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>1171811</v>
+      </c>
+      <c r="K21" s="7" t="n">
+        <v>0.0742</v>
+      </c>
       <c r="L21" s="8">
         <f>IF(G21="Y",F21*K21,0)</f>
         <v/>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>Check height/fit on outline; THT tabs help mechanically</t>
+          <t>Same part as the badge. Footprint drawn for 1.6 mm boards; check legs on 1.0 mm</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="15">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>HDMI</t>
+          <t>USB-C input</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>D_HDMI</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>HDMI ESD array</t>
+          <t>Buck inductor</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>HDMI-rated ESD array</t>
+          <t>FTC252012S2R2MBCA (2.2uH)</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Various</t>
+          <t>IND-SMD_L2.5-W2.0_MHCHL2520</t>
         </is>
       </c>
       <c r="F22" s="4" t="n">
@@ -1341,232 +1519,280 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H22" s="6" t="n"/>
-      <c r="I22" s="6" t="n"/>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="7" t="n"/>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>C5832372</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>773097</v>
+      </c>
+      <c r="K22" s="7" t="n">
+        <v>0.0341</v>
+      </c>
       <c r="L22" s="8">
         <f>IF(G22="Y",F22*K22,0)</f>
         <v/>
       </c>
       <c r="M22" s="3" t="n"/>
     </row>
-    <row r="23" ht="23.85" customHeight="1" s="15">
+    <row r="23" ht="15" customHeight="1" s="15">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>HDMI</t>
+          <t>USB-C input</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>R_HSTX</t>
+          <t>R8,R9</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>HSTX series resistors (4 pairs, GPIO12-19)</t>
+          <t>Resistor</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Per Adafruit Metro RP2350 HDMI section</t>
+          <t>0402WGF5101TCE (5.1k)</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>R0402</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H23" s="6" t="n"/>
-      <c r="I23" s="6" t="n"/>
-      <c r="J23" s="6" t="n"/>
-      <c r="K23" s="7" t="n"/>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>C25905</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>2237664</v>
+      </c>
+      <c r="K23" s="7" t="n">
+        <v>0.0009</v>
+      </c>
       <c r="L23" s="8">
         <f>IF(G23="Y",F23*K23,0)</f>
         <v/>
       </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>Confirm values against open schematic</t>
-        </is>
-      </c>
+      <c r="M23" s="3" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1" s="15">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>HDMI</t>
+          <t>USB-C input</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>R_DDC</t>
+          <t>R10,R11</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>DDC (I2C) pull-ups + HPD</t>
+          <t>Resistor</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Per HDMI section</t>
+          <t>0402WGF270JTCE (27R)</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>R0402</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H24" s="6" t="n"/>
-      <c r="I24" s="6" t="n"/>
-      <c r="J24" s="6" t="n"/>
-      <c r="K24" s="7" t="n"/>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>C25100</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>1738</v>
+      </c>
+      <c r="K24" s="7" t="n">
+        <v>0.001</v>
+      </c>
       <c r="L24" s="8">
         <f>IF(G24="Y",F24*K24,0)</f>
         <v/>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>Optional - only if reading monitor EDID</t>
+          <t>Low JLC stock (enough for small runs)</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="15">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>UI / Debug</t>
+          <t>USB-C input</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>SW1</t>
+          <t>R12,R16,R17,R18,R34,R35</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>BOOTSEL button</t>
+          <t>Resistor</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Tactile switch</t>
+          <t>0402WGF1003TCE (100k)</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>R0402</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H25" s="6" t="n"/>
-      <c r="I25" s="6" t="n"/>
-      <c r="J25" s="6" t="n"/>
-      <c r="K25" s="7" t="n"/>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>C25741</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>1535859</v>
+      </c>
+      <c r="K25" s="7" t="n">
+        <v>0.004</v>
+      </c>
       <c r="L25" s="8">
         <f>IF(G25="Y",F25*K25,0)</f>
         <v/>
       </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>Pulls flash CS low</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="23.85" customHeight="1" s="15">
+      <c r="M25" s="3" t="n"/>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="15">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>UI / Debug</t>
+          <t>USB-C input</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>R_SW1</t>
+          <t>R13,R15</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>BOOTSEL external pull-up</t>
+          <t>Resistor</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>0402WGF2202TCE (22k)</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>R0402</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H26" s="6" t="n"/>
-      <c r="I26" s="6" t="n"/>
-      <c r="J26" s="6" t="n"/>
-      <c r="K26" s="7" t="n"/>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>C25768</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>667275</v>
+      </c>
+      <c r="K26" s="7" t="n">
+        <v>0.0013</v>
+      </c>
       <c r="L26" s="8">
         <f>IF(G26="Y",F26*K26,0)</f>
         <v/>
       </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>Erratum RP2350-E9 workaround - internal pulls unreliable pre-A4 stepping</t>
-        </is>
-      </c>
+      <c r="M26" s="3" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1" s="15">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>UI / Debug</t>
+          <t>USB-C input</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>SW2</t>
+          <t>U3</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>RUN (reset) button</t>
+          <t>Buck 5V -&gt; 3V3 (2 A)</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Tactile switch</t>
+          <t>TLV62569DBVR</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>SOT-23-5_L3.0-W1.7-P0.95-LS2.8-BR</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
@@ -1577,40 +1803,52 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H27" s="6" t="n"/>
-      <c r="I27" s="6" t="n"/>
-      <c r="J27" s="6" t="n"/>
-      <c r="K27" s="7" t="n"/>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>C141836</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>108275</v>
+      </c>
+      <c r="K27" s="7" t="n">
+        <v>0.0733</v>
+      </c>
       <c r="L27" s="8">
         <f>IF(G27="Y",F27*K27,0)</f>
         <v/>
       </c>
       <c r="M27" s="3" t="n"/>
     </row>
-    <row r="28" ht="23.85" customHeight="1" s="15">
+    <row r="28" ht="15" customHeight="1" s="15">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>UI / Debug</t>
+          <t>USB-C input</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>R_SW2</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>RUN external pull-up</t>
+          <t>USB ESD</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>USBLC6-2SC6</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>SOT-23-6_L2.9-W1.6-P0.95-LS2.8-BL</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
@@ -1621,44 +1859,52 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H28" s="6" t="n"/>
-      <c r="I28" s="6" t="n"/>
-      <c r="J28" s="6" t="n"/>
-      <c r="K28" s="7" t="n"/>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>C2687116</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>150192</v>
+      </c>
+      <c r="K28" s="7" t="n">
+        <v>0.0476</v>
+      </c>
       <c r="L28" s="8">
         <f>IF(G28="Y",F28*K28,0)</f>
         <v/>
       </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>Standard practice for reset line + erratum RP2350-E9 workaround</t>
-        </is>
-      </c>
+      <c r="M28" s="3" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1" s="15">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>UI / Debug</t>
+          <t>Power mux</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>C_SW2</t>
+          <t>R14</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>RUN debounce cap</t>
+          <t>Resistor</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>100nF</t>
+          <t>0402WGF3302TCE (33k)</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>R0402</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
@@ -1669,44 +1915,52 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H29" s="6" t="n"/>
-      <c r="I29" s="6" t="n"/>
-      <c r="J29" s="6" t="n"/>
-      <c r="K29" s="7" t="n"/>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>C25779</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>897525</v>
+      </c>
+      <c r="K29" s="7" t="n">
+        <v>0.0008</v>
+      </c>
       <c r="L29" s="8">
         <f>IF(G29="Y",F29*K29,0)</f>
         <v/>
       </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t>To GND, for reset debounce</t>
-        </is>
-      </c>
+      <c r="M29" s="3" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1" s="15">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>UI / Debug</t>
+          <t>Power mux</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>SW3</t>
+          <t>U2</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>User button</t>
+          <t>Power mux, USB priority, reverse blocking</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Tactile switch</t>
+          <t>TPS2116DRLR</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>SOT-583-8_L2.1-W1.6-P0.50-LS1.6-BL</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
@@ -1717,44 +1971,52 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H30" s="6" t="n"/>
-      <c r="I30" s="6" t="n"/>
-      <c r="J30" s="6" t="n"/>
-      <c r="K30" s="7" t="n"/>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>C3235557</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>12811</v>
+      </c>
+      <c r="K30" s="7" t="n">
+        <v>0.5491</v>
+      </c>
       <c r="L30" s="8">
         <f>IF(G30="Y",F30*K30,0)</f>
         <v/>
       </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>Wire to a spare GPIO</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="23.85" customHeight="1" s="15">
+      <c r="M30" s="3" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="15">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>UI / Debug</t>
+          <t>HDMI +5V boost</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>R_SW3</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>User button external pull-up</t>
+          <t>HDMI +5V resettable fuse</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>JK-SMD0805-020-30V (200mA PTC)</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>F0805</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
@@ -1765,44 +2027,52 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H31" s="6" t="n"/>
-      <c r="I31" s="6" t="n"/>
-      <c r="J31" s="6" t="n"/>
-      <c r="K31" s="7" t="n"/>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>C516070</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>460152</v>
+      </c>
+      <c r="K31" s="7" t="n">
+        <v>0.031</v>
+      </c>
       <c r="L31" s="8">
         <f>IF(G31="Y",F31*K31,0)</f>
         <v/>
       </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t>Erratum RP2350-E9 workaround - internal pulls unreliable pre-A4 stepping</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="23.85" customHeight="1" s="15">
+      <c r="M31" s="3" t="n"/>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="15">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>UI / Debug</t>
+          <t>HDMI +5V boost</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>SWD debug header</t>
+          <t>Boost inductor</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>3-pin header (SWCLK, SWDIO, GND)</t>
+          <t>FTC252010S1R0MBCA (1uH)</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>2.54mm or Tag-Connect</t>
+          <t>IND-SMD_L2.5-W2.0_FTC252010S</t>
         </is>
       </c>
       <c r="F32" s="4" t="n">
@@ -1810,95 +2080,111 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="n"/>
-      <c r="I32" s="6" t="n"/>
-      <c r="J32" s="6" t="n"/>
-      <c r="K32" s="7" t="n"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>C5832356</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="n">
+        <v>259264</v>
+      </c>
+      <c r="K32" s="7" t="n">
+        <v>0.0396</v>
+      </c>
       <c r="L32" s="8">
         <f>IF(G32="Y",F32*K32,0)</f>
         <v/>
       </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>Footprint only; hand-solder if wanted</t>
-        </is>
-      </c>
+      <c r="M32" s="3" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1" s="15">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>UI / Debug</t>
+          <t>HDMI +5V boost</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>J4</t>
+          <t>R19,R29</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>I2C + spare GPIO pads / header</t>
+          <t>Resistor</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Pin header</t>
+          <t>0402WGF2003TCE (200k)</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>2.54mm</t>
+          <t>R0402</t>
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H33" s="6" t="n"/>
-      <c r="I33" s="6" t="n"/>
-      <c r="J33" s="6" t="n"/>
-      <c r="K33" s="7" t="n"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>C25764</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>268738</v>
+      </c>
+      <c r="K33" s="7" t="n">
+        <v>0.0009</v>
+      </c>
       <c r="L33" s="8">
         <f>IF(G33="Y",F33*K33,0)</f>
         <v/>
       </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>Footprint only</t>
-        </is>
-      </c>
+      <c r="M33" s="3" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1" s="15">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Indicators</t>
+          <t>HDMI +5V boost</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>D_3V3</t>
+          <t>R20</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>3V3 power indicator LED</t>
+          <t>Resistor</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Green LED, 2mA-class</t>
+          <t>0402WGF2702TCE (27k)</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>R0402</t>
         </is>
       </c>
       <c r="F34" s="4" t="n">
@@ -1909,44 +2195,52 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H34" s="6" t="n"/>
-      <c r="I34" s="6" t="n"/>
-      <c r="J34" s="6" t="n"/>
-      <c r="K34" s="7" t="n"/>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>C25771</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>Preferred</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v>153614</v>
+      </c>
+      <c r="K34" s="7" t="n">
+        <v>0.0011</v>
+      </c>
       <c r="L34" s="8">
         <f>IF(G34="Y",F34*K34,0)</f>
         <v/>
       </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t>On badge/board 3V3 rail</t>
-        </is>
-      </c>
+      <c r="M34" s="3" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1" s="15">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Indicators</t>
+          <t>HDMI +5V boost</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>R_3V3</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>3V3 LED series resistor</t>
+          <t>Boost 3V3 -&gt; 5V for HDMI pin 18</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>~1k (for 3.3V, 2mA green LED)</t>
+          <t>TPS61023DRLR</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>SOT-563_L1.6-W1.2-P0.50-LS1.6-BR</t>
         </is>
       </c>
       <c r="F35" s="4" t="n">
@@ -1957,44 +2251,52 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H35" s="6" t="n"/>
-      <c r="I35" s="6" t="n"/>
-      <c r="J35" s="6" t="n"/>
-      <c r="K35" s="7" t="n"/>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>C919459</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>16691</v>
+      </c>
+      <c r="K35" s="7" t="n">
+        <v>0.268</v>
+      </c>
       <c r="L35" s="8">
         <f>IF(G35="Y",F35*K35,0)</f>
         <v/>
       </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t>Recalc for actual LED Vf/If</t>
-        </is>
-      </c>
+      <c r="M35" s="3" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1" s="15">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Indicators</t>
+          <t>HDMI Type A</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>D_5V</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>5V power indicator LED</t>
+          <t>HDMI Type A receptacle</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Red or amber LED, 2mA-class</t>
+          <t>HDMI-001 19PCBTP (HDMI-A)</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>HDMI-SMD_19P-P0.50-H-F</t>
         </is>
       </c>
       <c r="F36" s="4" t="n">
@@ -2005,140 +2307,168 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H36" s="6" t="n"/>
-      <c r="I36" s="6" t="n"/>
-      <c r="J36" s="6" t="n"/>
-      <c r="K36" s="7" t="n"/>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>C138388</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="n">
+        <v>50039</v>
+      </c>
+      <c r="K36" s="7" t="n">
+        <v>0.2332</v>
+      </c>
       <c r="L36" s="8">
         <f>IF(G36="Y",F36*K36,0)</f>
         <v/>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>On 5V rail (from boost/USB); only if 5V present</t>
+          <t>Full-size HDMI Type A. Check fit on the board edge</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="15">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Indicators</t>
+          <t>HDMI Type A</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>R_5V</t>
+          <t>R30,R31,R48,R49,R50</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>5V LED series resistor</t>
+          <t>Resistor</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>~2.2k (for 5V, 2mA LED)</t>
+          <t>0402WGF4701TCE (4.7k)</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>R0402</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H37" s="6" t="n"/>
-      <c r="I37" s="6" t="n"/>
-      <c r="J37" s="6" t="n"/>
-      <c r="K37" s="7" t="n"/>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>C25900</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="n">
+        <v>3285378</v>
+      </c>
+      <c r="K37" s="7" t="n">
+        <v>0.0011</v>
+      </c>
       <c r="L37" s="8">
         <f>IF(G37="Y",F37*K37,0)</f>
         <v/>
       </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t>Recalc for actual LED Vf/If</t>
-        </is>
-      </c>
+      <c r="M37" s="3" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1" s="15">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Indicators</t>
+          <t>HDMI Type A</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>D_USR</t>
+          <t>R32,R33</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>User/status LED (GPIO-driven)</t>
+          <t>Resistor</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>LED, any colour</t>
+          <t>0402WGF2001TCE (2k)</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>R0402</t>
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H38" s="6" t="n"/>
-      <c r="I38" s="6" t="n"/>
-      <c r="J38" s="6" t="n"/>
-      <c r="K38" s="7" t="n"/>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>C4109</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="n">
+        <v>1661561</v>
+      </c>
+      <c r="K38" s="7" t="n">
+        <v>0.0008</v>
+      </c>
       <c r="L38" s="8">
         <f>IF(G38="Y",F38*K38,0)</f>
         <v/>
       </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>Drive from a spare GPIO</t>
-        </is>
-      </c>
+      <c r="M38" s="3" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1" s="15">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Indicators</t>
+          <t>HDMI Type A</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>R_USR</t>
+          <t>U5</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>User LED series resistor</t>
+          <t>HDMI DDC level shifter</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>~330 ohm (for 3.3V GPIO, ~5-10mA)</t>
+          <t>PCA9306DCUR</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>SSOP-8_L2.0-W2.3-P0.50-LS3.1-BR</t>
         </is>
       </c>
       <c r="F39" s="4" t="n">
@@ -2149,92 +2479,108 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H39" s="6" t="n"/>
-      <c r="I39" s="6" t="n"/>
-      <c r="J39" s="6" t="n"/>
-      <c r="K39" s="7" t="n"/>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>C33196</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="n">
+        <v>19803</v>
+      </c>
+      <c r="K39" s="7" t="n">
+        <v>0.3319</v>
+      </c>
       <c r="L39" s="8">
         <f>IF(G39="Y",F39*K39,0)</f>
         <v/>
       </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t>Recalc for chosen LED and GPIO drive current</t>
-        </is>
-      </c>
+      <c r="M39" s="3" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1" s="15">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Indicators</t>
+          <t>HDMI Type A</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>D_NP1</t>
+          <t>U6,U7</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>NeoPixel (WS2812/SK6812)</t>
+          <t>HDMI TMDS ESD (0.5 pF)</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Addressable RGB LED</t>
+          <t>TPD4E05U06DQAR</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>5050 SMD</t>
+          <t>USON-10_L2.5-W1.0-P0.50-BL</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H40" s="6" t="n"/>
-      <c r="I40" s="6" t="n"/>
-      <c r="J40" s="6" t="n"/>
-      <c r="K40" s="7" t="n"/>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>C138714</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="n">
+        <v>94387</v>
+      </c>
+      <c r="K40" s="7" t="n">
+        <v>0.0819</v>
+      </c>
       <c r="L40" s="8">
         <f>IF(G40="Y",F40*K40,0)</f>
         <v/>
       </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t>Qty placeholder - set to how many pixels wanted</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="23.85" customHeight="1" s="15">
+      <c r="M40" s="3" t="n"/>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="15">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Indicators</t>
+          <t>Hexpansion edge connector</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>R_NP_DATA</t>
+          <t>C29</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>NeoPixel data line series resistor</t>
+          <t>EEPROM decoupling</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>330-470 ohm</t>
+          <t>CL05B104KO5NNNC (100nF)</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>C0402</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
@@ -2242,47 +2588,59 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H41" s="6" t="n"/>
-      <c r="I41" s="6" t="n"/>
-      <c r="J41" s="6" t="n"/>
-      <c r="K41" s="7" t="n"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>C1525</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="n">
+        <v>16407331</v>
+      </c>
+      <c r="K41" s="7" t="n">
+        <v>0.006</v>
+      </c>
       <c r="L41" s="8">
         <f>IF(G41="Y",F41*K41,0)</f>
         <v/>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>Between GPIO and first pixel's DIN; protects against overshoot</t>
+          <t>DNP with U10</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="15">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Indicators</t>
+          <t>Hexpansion edge connector</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>C_NP</t>
+          <t>J6</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>NeoPixel decoupling cap</t>
+          <t>Hexpansion edge connector (PCB edge)</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>100nF-1uF per pixel, close to VDD/GND</t>
+          <t>Hexpansion-Connector</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>0402/0603</t>
+          <t>hexpansion-edge-connector</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
@@ -2290,7 +2648,7 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H42" s="6" t="n"/>
@@ -2303,34 +2661,34 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>One per pixel, placed right at the LED</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="23.85" customHeight="1" s="15">
+          <t>PCB edge fingers, no part</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="15">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Hexpansion</t>
+          <t>Hexpansion edge connector</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>ID EEPROM</t>
+          <t>Hexpansion ID EEPROM (fallback)</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Per hexpansion spec</t>
+          <t>ZD24C64A-SSGMT (ZD24C64A (fallback))</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>SOIC-8 / TSSOP-8</t>
+          <t>SOP-8_L4.9-W3.9-P1.27-LS6.0-BL</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
@@ -2341,58 +2699,82 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H43" s="6" t="n"/>
-      <c r="I43" s="6" t="n"/>
-      <c r="J43" s="6" t="n"/>
-      <c r="K43" s="7" t="n"/>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>C2896793</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="n">
+        <v>6312</v>
+      </c>
+      <c r="K43" s="7" t="n">
+        <v>0.1419</v>
+      </c>
       <c r="L43" s="8">
         <f>IF(G43="Y",F43*K43,0)</f>
         <v/>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>Footprint only - not populated; confirm part/address in spec</t>
+          <t>DNP. Fit only if EEPROM emulation fails</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="15">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Hexpansion</t>
+          <t>microSD</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>R_I2C</t>
+          <t>J4</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>I2C pull-ups</t>
+          <t>Qwiic</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Per bus voltage</t>
+          <t>SM04B-SRSS-TB(LF)(SN) (Qwiic)</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>CONN-SMD_4P-P1.00_SM04B-SRSS-TB-LF-SN</t>
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H44" s="6" t="n"/>
-      <c r="I44" s="6" t="n"/>
-      <c r="J44" s="6" t="n"/>
-      <c r="K44" s="7" t="n"/>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>C160404</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="n">
+        <v>7284</v>
+      </c>
+      <c r="K44" s="7" t="n">
+        <v>0.2262</v>
+      </c>
       <c r="L44" s="8">
         <f>IF(G44="Y",F44*K44,0)</f>
         <v/>
@@ -2402,160 +2784,565 @@
     <row r="45" ht="15" customHeight="1" s="15">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>microSD</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>TP1-TP3</t>
+          <t>J5</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Test points 3V3 / 5V / GND</t>
+          <t>microSD socket</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Test pads</t>
+          <t>TF-01A (microSD)</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>SMD pad</t>
+          <t>TF-SMD_TF-01A</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H45" s="6" t="n"/>
-      <c r="I45" s="6" t="n"/>
-      <c r="J45" s="6" t="n"/>
-      <c r="K45" s="7" t="n"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>C91145</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="n">
+        <v>165996</v>
+      </c>
+      <c r="K45" s="7" t="n">
+        <v>0.192</v>
+      </c>
       <c r="L45" s="8">
         <f>IF(G45="Y",F45*K45,0)</f>
         <v/>
       </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t>Bare pads, no assembly</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" s="15"/>
+      <c r="M45" s="3" t="n"/>
+    </row>
+    <row r="46" ht="15" customHeight="1" s="15">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>microSD</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>JP1</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Qwiic pull-up solder jumper</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Qwiic pull-ups</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>SolderJumper-2_P1.3mm_Bridged_RoundedPad1.0x1.5mm</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="n"/>
+      <c r="I46" s="6" t="n"/>
+      <c r="J46" s="6" t="n"/>
+      <c r="K46" s="7" t="n"/>
+      <c r="L46" s="8">
+        <f>IF(G46="Y",F46*K46,0)</f>
+        <v/>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Bare copper jumper, cut to remove Qwiic pull-ups</t>
+        </is>
+      </c>
+    </row>
     <row r="47" ht="15" customHeight="1" s="15">
-      <c r="K47" s="9" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>LEDs, test pads, mounting</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>H1,H2</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Mounting holes</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>MountingHole</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>MountingHole_2.2mm_M2_Pad_Via</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="n"/>
+      <c r="I47" s="6" t="n"/>
+      <c r="J47" s="6" t="n"/>
+      <c r="K47" s="7" t="n"/>
+      <c r="L47" s="8">
+        <f>IF(G47="Y",F47*K47,0)</f>
+        <v/>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Bare pads</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1" s="15">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>LEDs, test pads, mounting</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>LED1,LED2</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Power + status LEDs</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>KT-0603R (PWR/STATUS)</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>LED-SMD_L1.6-W0.8-R-RD</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>C2286</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="n">
+        <v>8154450</v>
+      </c>
+      <c r="K48" s="7" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="L48" s="8">
+        <f>IF(G48="Y",F48*K48,0)</f>
+        <v/>
+      </c>
+      <c r="M48" s="3" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="15">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>LEDs, test pads, mounting</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>LED3</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>RGB status LED</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>SK6805MICRO-J</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>LED-SMD_4P-L2.7-W2.4_SK6805MICRO-J</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>C2909056</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>38882</v>
+      </c>
+      <c r="K49" s="7" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="L49" s="8">
+        <f>IF(G49="Y",F49*K49,0)</f>
+        <v/>
+      </c>
+      <c r="M49" s="3" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1" s="15">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>LEDs, test pads, mounting</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>R52</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>0402WGF3300TCE (330R)</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>R0402</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>C25104</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="n">
+        <v>732878</v>
+      </c>
+      <c r="K50" s="7" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="L50" s="8">
+        <f>IF(G50="Y",F50*K50,0)</f>
+        <v/>
+      </c>
+      <c r="M50" s="3" t="n"/>
+    </row>
+    <row r="51" ht="15" customHeight="1" s="15">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>LEDs, test pads, mounting</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>TP1</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Test pad</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>+3V3</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>TestPoint_Pad_D1.0mm</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="n"/>
+      <c r="I51" s="6" t="n"/>
+      <c r="J51" s="6" t="n"/>
+      <c r="K51" s="7" t="n"/>
+      <c r="L51" s="8">
+        <f>IF(G51="Y",F51*K51,0)</f>
+        <v/>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Bare pads</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1" s="15">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>LEDs, test pads, mounting</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>TP2</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Test pad</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>V5_HDMI</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>TestPoint_Pad_D1.0mm</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="n"/>
+      <c r="I52" s="6" t="n"/>
+      <c r="J52" s="6" t="n"/>
+      <c r="K52" s="7" t="n"/>
+      <c r="L52" s="8">
+        <f>IF(G52="Y",F52*K52,0)</f>
+        <v/>
+      </c>
+      <c r="M52" s="3" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1" s="15">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>LEDs, test pads, mounting</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>TP3</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Test pad</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>GND</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>TestPoint_Pad_D1.0mm</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="n"/>
+      <c r="I53" s="6" t="n"/>
+      <c r="J53" s="6" t="n"/>
+      <c r="K53" s="7" t="n"/>
+      <c r="L53" s="8">
+        <f>IF(G53="Y",F53*K53,0)</f>
+        <v/>
+      </c>
+      <c r="M53" s="3" t="n"/>
+    </row>
+    <row r="54" s="15"/>
+    <row r="55" ht="15" customHeight="1" s="15">
+      <c r="K55" s="9" t="inlineStr">
         <is>
           <t>Assembled line items</t>
         </is>
       </c>
-      <c r="L47" s="10">
-        <f>COUNTIF(G5:G45,"Y")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="15" customHeight="1" s="15">
-      <c r="K48" s="9" t="inlineStr">
+      <c r="L55" s="10">
+        <f>COUNTIF(G5:G53,"Y")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1" s="15">
+      <c r="K56" s="9" t="inlineStr">
         <is>
           <t>Unique Extended parts (setup fee each)</t>
         </is>
       </c>
-      <c r="L48" s="10">
-        <f>COUNTIF(I5:I45,"Extended")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="15">
-      <c r="K49" s="9" t="inlineStr">
+      <c r="L56" s="10">
+        <f>COUNTIF(I5:I53,"Extended")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1" s="15">
+      <c r="K57" s="9" t="inlineStr">
         <is>
           <t>Assembly setup fee (USD)</t>
         </is>
       </c>
-      <c r="L49" s="11" t="n">
+      <c r="L57" s="11" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1" s="15">
-      <c r="K50" s="9" t="inlineStr">
+    <row r="58" ht="15" customHeight="1" s="15">
+      <c r="K58" s="9" t="inlineStr">
         <is>
           <t>Extended fee per part (USD)</t>
         </is>
       </c>
-      <c r="L50" s="11" t="n">
+      <c r="L58" s="11" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="51" ht="15" customHeight="1" s="15">
-      <c r="K51" s="9" t="inlineStr">
+    <row r="59" ht="15" customHeight="1" s="15">
+      <c r="K59" s="9" t="inlineStr">
         <is>
           <t>Extended parts fee (USD)</t>
         </is>
       </c>
-      <c r="L51" s="12">
-        <f>L48*L50</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="15" customHeight="1" s="15">
-      <c r="K52" s="9" t="inlineStr">
+      <c r="L59" s="12">
+        <f>L56*L58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1" s="15">
+      <c r="K60" s="9" t="inlineStr">
         <is>
           <t>Parts cost per board (USD)</t>
         </is>
       </c>
-      <c r="L52" s="12">
-        <f>SUM(L5:L45)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="15" customHeight="1" s="15">
-      <c r="K53" s="9" t="inlineStr">
+      <c r="L60" s="12">
+        <f>SUM(L5:L53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1" s="15">
+      <c r="K61" s="9" t="inlineStr">
         <is>
           <t>Boards in run</t>
         </is>
       </c>
-      <c r="L53" s="13" t="n">
+      <c r="L61" s="13" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="54" ht="15" customHeight="1" s="15">
-      <c r="K54" s="9" t="inlineStr">
+    <row r="62" ht="15" customHeight="1" s="15">
+      <c r="K62" s="9" t="inlineStr">
         <is>
           <t>Parts cost for run (USD)</t>
         </is>
       </c>
-      <c r="L54" s="12">
-        <f>L52*L53</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="15" customHeight="1" s="15">
-      <c r="K55" s="14" t="inlineStr">
+      <c r="L62" s="12">
+        <f>L60*L61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1" s="15">
+      <c r="K63" s="14" t="inlineStr">
         <is>
           <t>Assumptions: setup fee and Extended fee are placeholders I entered (roughly typical JLCPCB figures, not verified) - update from the current JLCPCB pricing page. Board count is 5 as suggested; PCB fabrication and shipping/VAT are not included.</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="15" customHeight="1" s="15"/>
-    <row r="57" ht="15" customHeight="1" s="15"/>
-    <row r="58" s="15"/>
+    <row r="64" ht="15" customHeight="1" s="15"/>
+    <row r="65" ht="15" customHeight="1" s="15"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:M2"/>
-    <mergeCell ref="K55:M57"/>
+    <mergeCell ref="K63:M65"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="G5:G45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="G5:G53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="I5:I45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Basic,Extended,Not at LCSC"</formula1>
-      <formula2>0</formula2>
+    <dataValidation sqref="I5:I53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Basic,Preferred,Extended,Not at LCSC"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/hardware/hexpansion_bom.xlsx
+++ b/hardware/hexpansion_bom.xlsx
@@ -406,7 +406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="15" min="1" max="2"/>
@@ -513,7 +513,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>C1,C2,C3,C4,C5,C6,C7,C8,C9,C10,C11,C12,C19,C20,C27,C28,C30,C32</t>
+          <t>C1,C2,C3,C4,C5,C6,C7,C10,C11,C12,C20,C32</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
@@ -569,7 +569,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>C13,C14,C15,C31</t>
+          <t>C13,C14,C15</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
       </c>
       <c r="M12" s="3" t="n"/>
     </row>
-    <row r="13" ht="23.85" customHeight="1" s="15">
+    <row r="13" ht="15" customHeight="1" s="15">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Core</t>
@@ -969,7 +969,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>R3,R5,R7,R41,R42,R43,R44,R45,R46,R47</t>
+          <t>R3,R7,R41</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="M13" s="3" t="n"/>
     </row>
-    <row r="14" ht="23.85" customHeight="1" s="15">
+    <row r="14" ht="15" customHeight="1" s="15">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Core</t>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>R4,R21,R22,R23,R24,R25,R26,R27,R28</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1044,7 +1044,7 @@
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>R19,R29</t>
+          <t>R19</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
@@ -2341,26 +2341,26 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>R30,R31,R48,R49,R50</t>
+          <t>U6,U7</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Resistor</t>
+          <t>HDMI TMDS ESD (0.5 pF)</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>0402WGF4701TCE (4.7k)</t>
+          <t>TPD4E05U06DQAR</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>R0402</t>
+          <t>USON-10_L2.5-W1.0-P0.50-BL</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
@@ -2369,19 +2369,19 @@
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>C25900</t>
+          <t>C138714</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="J37" s="6" t="n">
-        <v>3285378</v>
+        <v>94387</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>0.0011</v>
+        <v>0.0819</v>
       </c>
       <c r="L37" s="8">
         <f>IF(G37="Y",F37*K37,0)</f>
@@ -2392,40 +2392,40 @@
     <row r="38" ht="15" customHeight="1" s="15">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>HDMI Type A</t>
+          <t>Hexpansion edge connector</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>R32,R33</t>
+          <t>C29</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Resistor</t>
+          <t>EEPROM decoupling</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>0402WGF2001TCE (2k)</t>
+          <t>CL05B104KO5NNNC (100nF)</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>R0402</t>
+          <t>C0402</t>
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>C4109</t>
+          <t>C1525</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
@@ -2434,41 +2434,45 @@
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1661561</v>
+        <v>16407331</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>0.0008</v>
+        <v>0.006</v>
       </c>
       <c r="L38" s="8">
         <f>IF(G38="Y",F38*K38,0)</f>
         <v/>
       </c>
-      <c r="M38" s="3" t="n"/>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>DNP with U10</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="15">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>HDMI Type A</t>
+          <t>Hexpansion edge connector</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>J6</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>HDMI DDC level shifter</t>
+          <t>Hexpansion edge connector (PCB edge)</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>PCA9306DCUR</t>
+          <t>Hexpansion-Connector</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>SSOP-8_L2.0-W2.3-P0.50-LS3.1-BR</t>
+          <t>hexpansion-edge-connector</t>
         </is>
       </c>
       <c r="F39" s="4" t="n">
@@ -2476,68 +2480,60 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>C33196</t>
-        </is>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J39" s="6" t="n">
-        <v>19803</v>
-      </c>
-      <c r="K39" s="7" t="n">
-        <v>0.3319</v>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="n"/>
+      <c r="I39" s="6" t="n"/>
+      <c r="J39" s="6" t="n"/>
+      <c r="K39" s="7" t="n"/>
       <c r="L39" s="8">
         <f>IF(G39="Y",F39*K39,0)</f>
         <v/>
       </c>
-      <c r="M39" s="3" t="n"/>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>PCB edge fingers, no part</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="15">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>HDMI Type A</t>
+          <t>Hexpansion edge connector</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>U6,U7</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>HDMI TMDS ESD (0.5 pF)</t>
+          <t>Hexpansion ID EEPROM (fallback)</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>TPD4E05U06DQAR</t>
+          <t>ZD24C64A-SSGMT (ZD24C64A (fallback))</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>USON-10_L2.5-W1.0-P0.50-BL</t>
+          <t>SOP-8_L4.9-W3.9-P1.27-LS6.0-BL</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>C138714</t>
+          <t>C2896793</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
@@ -2546,149 +2542,149 @@
         </is>
       </c>
       <c r="J40" s="6" t="n">
-        <v>94387</v>
+        <v>6312</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>0.0819</v>
+        <v>0.1419</v>
       </c>
       <c r="L40" s="8">
         <f>IF(G40="Y",F40*K40,0)</f>
         <v/>
       </c>
-      <c r="M40" s="3" t="n"/>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>DNP. Fit only if EEPROM emulation fails</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="15">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Hexpansion edge connector</t>
+          <t>LEDs, test pads, mounting</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>C29</t>
+          <t>H1,H2</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>EEPROM decoupling</t>
+          <t>Mounting holes</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>CL05B104KO5NNNC (100nF)</t>
+          <t>MountingHole</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>C0402</t>
+          <t>MountingHole_2.2mm_M2_Pad_Via</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H41" s="6" t="inlineStr">
-        <is>
-          <t>C1525</t>
-        </is>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="J41" s="6" t="n">
-        <v>16407331</v>
-      </c>
-      <c r="K41" s="7" t="n">
-        <v>0.006</v>
-      </c>
+      <c r="H41" s="6" t="n"/>
+      <c r="I41" s="6" t="n"/>
+      <c r="J41" s="6" t="n"/>
+      <c r="K41" s="7" t="n"/>
       <c r="L41" s="8">
         <f>IF(G41="Y",F41*K41,0)</f>
         <v/>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>DNP with U10</t>
+          <t>Bare pads</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="15">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Hexpansion edge connector</t>
+          <t>LEDs, test pads, mounting</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>J6</t>
+          <t>LED1,LED2</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Hexpansion edge connector (PCB edge)</t>
+          <t>Power + status LEDs</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Hexpansion-Connector</t>
+          <t>KT-0603R (PWR/STATUS)</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>hexpansion-edge-connector</t>
+          <t>LED-SMD_L1.6-W0.8-R-RD</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H42" s="6" t="n"/>
-      <c r="I42" s="6" t="n"/>
-      <c r="J42" s="6" t="n"/>
-      <c r="K42" s="7" t="n"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>C2286</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="n">
+        <v>8154450</v>
+      </c>
+      <c r="K42" s="7" t="n">
+        <v>0.0073</v>
+      </c>
       <c r="L42" s="8">
         <f>IF(G42="Y",F42*K42,0)</f>
         <v/>
       </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t>PCB edge fingers, no part</t>
-        </is>
-      </c>
+      <c r="M42" s="3" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1" s="15">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Hexpansion edge connector</t>
+          <t>LEDs, test pads, mounting</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>LED3</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Hexpansion ID EEPROM (fallback)</t>
+          <t>RGB status LED</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>ZD24C64A-SSGMT (ZD24C64A (fallback))</t>
+          <t>SK6805MICRO-J</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>SOP-8_L4.9-W3.9-P1.27-LS6.0-BL</t>
+          <t>LED-SMD_4P-L2.7-W2.4_SK6805MICRO-J</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
@@ -2696,12 +2692,12 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>C2896793</t>
+          <t>C2909056</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
@@ -2710,45 +2706,41 @@
         </is>
       </c>
       <c r="J43" s="6" t="n">
-        <v>6312</v>
+        <v>38882</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>0.1419</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="L43" s="8">
         <f>IF(G43="Y",F43*K43,0)</f>
         <v/>
       </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t>DNP. Fit only if EEPROM emulation fails</t>
-        </is>
-      </c>
+      <c r="M43" s="3" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1" s="15">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>microSD</t>
+          <t>LEDs, test pads, mounting</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>J4</t>
+          <t>R52</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Qwiic</t>
+          <t>Resistor</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>SM04B-SRSS-TB(LF)(SN) (Qwiic)</t>
+          <t>0402WGF3300TCE (330R)</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>CONN-SMD_4P-P1.00_SM04B-SRSS-TB-LF-SN</t>
+          <t>R0402</t>
         </is>
       </c>
       <c r="F44" s="4" t="n">
@@ -2761,19 +2753,19 @@
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>C160404</t>
+          <t>C25104</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="J44" s="6" t="n">
-        <v>7284</v>
+        <v>732878</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>0.2262</v>
+        <v>0.0012</v>
       </c>
       <c r="L44" s="8">
         <f>IF(G44="Y",F44*K44,0)</f>
@@ -2784,27 +2776,27 @@
     <row r="45" ht="15" customHeight="1" s="15">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>microSD</t>
+          <t>LEDs, test pads, mounting</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>J5</t>
+          <t>TP1</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>microSD socket</t>
+          <t>Test pad</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>TF-01A (microSD)</t>
+          <t>+3V3</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>TF-SMD_TF-01A</t>
+          <t>TestPoint_Pad_D1.0mm</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
@@ -2812,55 +2804,47 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>C91145</t>
-        </is>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J45" s="6" t="n">
-        <v>165996</v>
-      </c>
-      <c r="K45" s="7" t="n">
-        <v>0.192</v>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="n"/>
+      <c r="I45" s="6" t="n"/>
+      <c r="J45" s="6" t="n"/>
+      <c r="K45" s="7" t="n"/>
       <c r="L45" s="8">
         <f>IF(G45="Y",F45*K45,0)</f>
         <v/>
       </c>
-      <c r="M45" s="3" t="n"/>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Bare pads</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="15">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>microSD</t>
+          <t>LEDs, test pads, mounting</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>JP1</t>
+          <t>TP2</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Qwiic pull-up solder jumper</t>
+          <t>Test pad</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Qwiic pull-ups</t>
+          <t>V5_HDMI</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>SolderJumper-2_P1.3mm_Bridged_RoundedPad1.0x1.5mm</t>
+          <t>TestPoint_Pad_D1.0mm</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
@@ -2879,11 +2863,7 @@
         <f>IF(G46="Y",F46*K46,0)</f>
         <v/>
       </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t>Bare copper jumper, cut to remove Qwiic pull-ups</t>
-        </is>
-      </c>
+      <c r="M46" s="3" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1" s="15">
       <c r="A47" s="3" t="inlineStr">
@@ -2893,26 +2873,26 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>H1,H2</t>
+          <t>TP3</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Mounting holes</t>
+          <t>Test pad</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>MountingHole</t>
+          <t>GND</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>MountingHole_2.2mm_M2_Pad_Via</t>
+          <t>TestPoint_Pad_D1.0mm</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
@@ -2927,40 +2907,36 @@
         <f>IF(G47="Y",F47*K47,0)</f>
         <v/>
       </c>
-      <c r="M47" s="3" t="inlineStr">
-        <is>
-          <t>Bare pads</t>
-        </is>
-      </c>
+      <c r="M47" s="3" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1" s="15">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>LEDs, test pads, mounting</t>
+          <t>Qwiic</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>LED1,LED2</t>
+          <t>J4</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Power + status LEDs</t>
+          <t>Qwiic</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>KT-0603R (PWR/STATUS)</t>
+          <t>SM04B-SRSS-TB(LF)(SN) (Qwiic)</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>LED-SMD_L1.6-W0.8-R-RD</t>
+          <t>CONN-SMD_4P-P1.00_SM04B-SRSS-TB-LF-SN</t>
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
@@ -2969,19 +2945,19 @@
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>C2286</t>
+          <t>C160404</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="J48" s="6" t="n">
-        <v>8154450</v>
+        <v>7284</v>
       </c>
       <c r="K48" s="7" t="n">
-        <v>0.0073</v>
+        <v>0.2262</v>
       </c>
       <c r="L48" s="8">
         <f>IF(G48="Y",F48*K48,0)</f>
@@ -2992,27 +2968,27 @@
     <row r="49" ht="15" customHeight="1" s="15">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>LEDs, test pads, mounting</t>
+          <t>Qwiic</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>LED3</t>
+          <t>JP1</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>RGB status LED</t>
+          <t>Qwiic pull-up solder jumper</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>SK6805MICRO-J</t>
+          <t>Qwiic pull-ups</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>LED-SMD_4P-L2.7-W2.4_SK6805MICRO-J</t>
+          <t>SolderJumper-2_P1.3mm_Bridged_RoundedPad1.0x1.5mm</t>
         </is>
       </c>
       <c r="F49" s="4" t="n">
@@ -3020,40 +2996,32 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>C2909056</t>
-        </is>
-      </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="J49" s="6" t="n">
-        <v>38882</v>
-      </c>
-      <c r="K49" s="7" t="n">
-        <v>0.08989999999999999</v>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="n"/>
+      <c r="I49" s="6" t="n"/>
+      <c r="J49" s="6" t="n"/>
+      <c r="K49" s="7" t="n"/>
       <c r="L49" s="8">
         <f>IF(G49="Y",F49*K49,0)</f>
         <v/>
       </c>
-      <c r="M49" s="3" t="n"/>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Bare copper jumper, cut to remove Qwiic pull-ups</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="15">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>LEDs, test pads, mounting</t>
+          <t>Qwiic</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>R52</t>
+          <t>R48,R49,R50</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -3063,7 +3031,7 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>0402WGF3300TCE (330R)</t>
+          <t>0402WGF4701TCE (4.7k)</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -3072,7 +3040,7 @@
         </is>
       </c>
       <c r="F50" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
@@ -3081,7 +3049,7 @@
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>C25104</t>
+          <t>C25900</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr">
@@ -3090,10 +3058,10 @@
         </is>
       </c>
       <c r="J50" s="6" t="n">
-        <v>732878</v>
+        <v>3285378</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>0.0012</v>
+        <v>0.0011</v>
       </c>
       <c r="L50" s="8">
         <f>IF(G50="Y",F50*K50,0)</f>
@@ -3101,247 +3069,114 @@
       </c>
       <c r="M50" s="3" t="n"/>
     </row>
-    <row r="51" ht="15" customHeight="1" s="15">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>LEDs, test pads, mounting</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>TP1</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>Test pad</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>+3V3</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>TestPoint_Pad_D1.0mm</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H51" s="6" t="n"/>
-      <c r="I51" s="6" t="n"/>
-      <c r="J51" s="6" t="n"/>
-      <c r="K51" s="7" t="n"/>
-      <c r="L51" s="8">
-        <f>IF(G51="Y",F51*K51,0)</f>
-        <v/>
-      </c>
-      <c r="M51" s="3" t="inlineStr">
-        <is>
-          <t>Bare pads</t>
-        </is>
-      </c>
-    </row>
+    <row r="51" s="15"/>
     <row r="52" ht="15" customHeight="1" s="15">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>LEDs, test pads, mounting</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>TP2</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>Test pad</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>V5_HDMI</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>TestPoint_Pad_D1.0mm</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H52" s="6" t="n"/>
-      <c r="I52" s="6" t="n"/>
-      <c r="J52" s="6" t="n"/>
-      <c r="K52" s="7" t="n"/>
-      <c r="L52" s="8">
-        <f>IF(G52="Y",F52*K52,0)</f>
-        <v/>
-      </c>
-      <c r="M52" s="3" t="n"/>
+      <c r="K52" s="9" t="inlineStr">
+        <is>
+          <t>Assembled line items</t>
+        </is>
+      </c>
+      <c r="L52" s="10">
+        <f>COUNTIF(G5:G50,"Y")</f>
+        <v/>
+      </c>
     </row>
     <row r="53" ht="15" customHeight="1" s="15">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>LEDs, test pads, mounting</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>TP3</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>Test pad</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>GND</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>TestPoint_Pad_D1.0mm</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H53" s="6" t="n"/>
-      <c r="I53" s="6" t="n"/>
-      <c r="J53" s="6" t="n"/>
-      <c r="K53" s="7" t="n"/>
-      <c r="L53" s="8">
-        <f>IF(G53="Y",F53*K53,0)</f>
-        <v/>
-      </c>
-      <c r="M53" s="3" t="n"/>
-    </row>
-    <row r="54" s="15"/>
+      <c r="K53" s="9" t="inlineStr">
+        <is>
+          <t>Unique Extended parts (setup fee each)</t>
+        </is>
+      </c>
+      <c r="L53" s="10">
+        <f>COUNTIF(I5:I50,"Extended")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1" s="15">
+      <c r="K54" s="9" t="inlineStr">
+        <is>
+          <t>Assembly setup fee (USD)</t>
+        </is>
+      </c>
+      <c r="L54" s="11" t="n">
+        <v>8</v>
+      </c>
+    </row>
     <row r="55" ht="15" customHeight="1" s="15">
       <c r="K55" s="9" t="inlineStr">
         <is>
-          <t>Assembled line items</t>
-        </is>
-      </c>
-      <c r="L55" s="10">
-        <f>COUNTIF(G5:G53,"Y")</f>
-        <v/>
+          <t>Extended fee per part (USD)</t>
+        </is>
+      </c>
+      <c r="L55" s="11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="15">
       <c r="K56" s="9" t="inlineStr">
         <is>
-          <t>Unique Extended parts (setup fee each)</t>
-        </is>
-      </c>
-      <c r="L56" s="10">
-        <f>COUNTIF(I5:I53,"Extended")</f>
+          <t>Extended parts fee (USD)</t>
+        </is>
+      </c>
+      <c r="L56" s="12">
+        <f>L53*L55</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="15">
       <c r="K57" s="9" t="inlineStr">
         <is>
-          <t>Assembly setup fee (USD)</t>
-        </is>
-      </c>
-      <c r="L57" s="11" t="n">
-        <v>8</v>
+          <t>Parts cost per board (USD)</t>
+        </is>
+      </c>
+      <c r="L57" s="12">
+        <f>SUM(L5:L50)</f>
+        <v/>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="15">
       <c r="K58" s="9" t="inlineStr">
         <is>
-          <t>Extended fee per part (USD)</t>
-        </is>
-      </c>
-      <c r="L58" s="11" t="n">
-        <v>3</v>
+          <t>Boards in run</t>
+        </is>
+      </c>
+      <c r="L58" s="13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="15">
       <c r="K59" s="9" t="inlineStr">
         <is>
-          <t>Extended parts fee (USD)</t>
+          <t>Parts cost for run (USD)</t>
         </is>
       </c>
       <c r="L59" s="12">
-        <f>L56*L58</f>
+        <f>L57*L58</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" s="15">
-      <c r="K60" s="9" t="inlineStr">
-        <is>
-          <t>Parts cost per board (USD)</t>
-        </is>
-      </c>
-      <c r="L60" s="12">
-        <f>SUM(L5:L53)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" ht="15" customHeight="1" s="15">
-      <c r="K61" s="9" t="inlineStr">
-        <is>
-          <t>Boards in run</t>
-        </is>
-      </c>
-      <c r="L61" s="13" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="62" ht="15" customHeight="1" s="15">
-      <c r="K62" s="9" t="inlineStr">
-        <is>
-          <t>Parts cost for run (USD)</t>
-        </is>
-      </c>
-      <c r="L62" s="12">
-        <f>L60*L61</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" ht="15" customHeight="1" s="15">
-      <c r="K63" s="14" t="inlineStr">
+      <c r="K60" s="14" t="inlineStr">
         <is>
           <t>Assumptions: setup fee and Extended fee are placeholders I entered (roughly typical JLCPCB figures, not verified) - update from the current JLCPCB pricing page. Board count is 5 as suggested; PCB fabrication and shipping/VAT are not included.</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="15" customHeight="1" s="15"/>
-    <row r="65" ht="15" customHeight="1" s="15"/>
+    <row r="61" ht="15" customHeight="1" s="15"/>
+    <row r="62" ht="15" customHeight="1" s="15"/>
+    <row r="63" s="15"/>
+    <row r="64" s="15"/>
+    <row r="65" s="15"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:M2"/>
-    <mergeCell ref="K63:M65"/>
+    <mergeCell ref="K60:M62"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="G5:G53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="I5:I53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I5:I50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Basic,Preferred,Extended,Not at LCSC"</formula1>
     </dataValidation>
   </dataValidations>

--- a/hardware/hexpansion_bom.xlsx
+++ b/hardware/hexpansion_bom.xlsx
@@ -406,7 +406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="15" min="1" max="2"/>
@@ -513,7 +513,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>C1,C2,C3,C4,C5,C6,C7,C10,C11,C12,C20,C32</t>
+          <t>C1,C2,C3,C4,C5,C6,C7,C10,C11,C12,C20,C32,C33</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>R3,R7,R41</t>
+          <t>R3,R4,R7,R41</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
@@ -1025,26 +1025,26 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>SW1,SW2</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Resistor</t>
+          <t>BOOTSEL + RESET buttons</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>0402WGF0000TCE (0R)</t>
+          <t>TS-1088-AR02016 (BOOTSEL/RESET)</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>R0402</t>
+          <t>SW-SMD_L3.9-W3.0-P4.45</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>C17168</t>
+          <t>C720477</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1062,20 +1062,16 @@
         </is>
       </c>
       <c r="J14" s="6" t="n">
-        <v>3956017</v>
+        <v>877449</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>0.0011</v>
+        <v>0.0557</v>
       </c>
       <c r="L14" s="8">
         <f>IF(G14="Y",F14*K14,0)</f>
         <v/>
       </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>R4 = LS_A to RUN link (see schematic notes)</t>
-        </is>
-      </c>
+      <c r="M14" s="3" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1" s="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1085,26 +1081,26 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>SW1,SW2</t>
+          <t>U1</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>BOOTSEL + RESET buttons</t>
+          <t>Microcontroller, 2 MB flash in package</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>TS-1088-AR02016 (BOOTSEL/RESET)</t>
+          <t>RP2354A</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>SW-SMD_L3.9-W3.0-P4.45</t>
+          <t>QFN-60_L7.0-W7.0-P0.40-TL-EP3.4</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
@@ -1113,27 +1109,31 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>C720477</t>
+          <t>C41378174</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="J15" s="6" t="n">
-        <v>877449</v>
+        <v>6193</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.0557</v>
+        <v>1.3097</v>
       </c>
       <c r="L15" s="8">
         <f>IF(G15="Y",F15*K15,0)</f>
         <v/>
       </c>
-      <c r="M15" s="3" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="15">
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Unit price from JLC list; you quoted GBP 1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="23.85" customHeight="1" s="15">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Core</t>
@@ -1141,22 +1141,22 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Microcontroller, 2 MB flash in package</t>
+          <t>QSPI PSRAM 8 MB (hand-solder)</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>RP2354A</t>
+          <t>APS6404L-3SQR-SN</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>QFN-60_L7.0-W7.0-P0.40-TL-EP3.4</t>
+          <t>SOIC-8_L4.9-W3.9-P1.27-LS6.0-BL</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>C41378174</t>
+          <t>C5333729</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="J16" s="6" t="n">
-        <v>6193</v>
+        <v>41</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>1.3097</v>
+        <v>4.3423</v>
       </c>
       <c r="L16" s="8">
         <f>IF(G16="Y",F16*K16,0)</f>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>Unit price from JLC list; you quoted GBP 1.00</t>
+          <t>DNP. SOP-8 3.3 V part (the -ZR is USON-8). Buy separately for hand soldering</t>
         </is>
       </c>
     </row>
@@ -1201,22 +1201,22 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>QSPI PSRAM 8 MB (hand-solder)</t>
+          <t>Badge LS_A -&gt; RUN open-drain buffer</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>APS6404L-3SQR-SN</t>
+          <t>SN74LVC1G07DBVR</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>SOIC-8_L4.9-W3.9-P1.27-LS6.0-BL</t>
+          <t>SOT-23-5_L3.0-W1.7-P0.95-LS2.8-BR</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>C5333729</t>
+          <t>C7829</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="J17" s="6" t="n">
-        <v>41</v>
+        <v>46270</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>4.3423</v>
+        <v>0.0915</v>
       </c>
       <c r="L17" s="8">
         <f>IF(G17="Y",F17*K17,0)</f>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>DNP. SOP-8 3.3 V part (the -ZR is USON-8). Buy separately for hand soldering</t>
+          <t>Badge reset buffer, powered from the badge rail (no backfeed)</t>
         </is>
       </c>
     </row>

--- a/hardware/hexpansion_bom.xlsx
+++ b/hardware/hexpansion_bom.xlsx
@@ -2281,7 +2281,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>J5</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>J6</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
